--- a/graficos/BERT_mejores_porc.xlsx
+++ b/graficos/BERT_mejores_porc.xlsx
@@ -49,58 +49,58 @@
     <t>comisión_lim</t>
   </si>
   <si>
-    <t>denuncia_dictamen_bert</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dictamen_bert_K3_0.05</t>
-  </si>
-  <si>
-    <t>denuncia_dictamen</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dictamen_K3_0.05</t>
+    <t>antecedentes_dictamen_bert</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dictamen_bert_K3_0.05</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dictamen_K3_0.05</t>
   </si>
   <si>
     <t>orps_lim</t>
   </si>
   <si>
-    <t>orps_lim_denuncia_dictamen_K6_0.05</t>
+    <t>orps_lim_antecedentes_dictamen_K6_0.05</t>
   </si>
   <si>
     <t>comisión</t>
   </si>
   <si>
-    <t>comisión_denuncia_dictamen_K7_0.05</t>
+    <t>comisión_antecedentes_dictamen_bert_K7_0.05</t>
   </si>
   <si>
     <t>orps</t>
   </si>
   <si>
-    <t>orps_denuncia_dictamen_K7_0.05</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_dictamen_bert_K7_0.05</t>
+    <t>orps_antecedentes_dictamen_K7_0.05</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_dictamen_K7_0.05</t>
   </si>
   <si>
     <t>todos</t>
   </si>
   <si>
-    <t>denuncia_bert</t>
-  </si>
-  <si>
-    <t>todos_denuncia_bert_K12_0.01</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_dictamen_bert_K8_0.05</t>
-  </si>
-  <si>
-    <t>denuncia</t>
-  </si>
-  <si>
-    <t>todos_denuncia_K5_0.05</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_dictamen_K15_0.01</t>
+    <t>antecedentes_bert</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_bert_K12_0.01</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_dictamen_bert_K8_0.05</t>
+  </si>
+  <si>
+    <t>antecedentes</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_K5_0.05</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_dictamen_K15_0.01</t>
   </si>
   <si>
     <t>dictamen</t>
@@ -109,31 +109,31 @@
     <t>orps_dictamen_K5_0.05</t>
   </si>
   <si>
-    <t>orps_lim_denuncia_bert_K6_0.05</t>
-  </si>
-  <si>
-    <t>todos_denuncia_bert_K6_0.05</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_K6_0.05</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_bert_K5_0.05</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_K5_0.05</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_K7_0.05</t>
-  </si>
-  <si>
-    <t>orps_denuncia_bert_K7_0.05</t>
-  </si>
-  <si>
-    <t>orps_denuncia_K7_0.05</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_bert_K7_0.05</t>
+    <t>orps_lim_antecedentes_bert_K6_0.05</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_bert_K6_0.05</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_K6_0.05</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_K5_0.05</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_bert_K5_0.05</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_K7_0.05</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_bert_K7_0.05</t>
+  </si>
+  <si>
+    <t>orps_antecedentes_bert_K7_0.05</t>
+  </si>
+  <si>
+    <t>orps_antecedentes_K7_0.05</t>
   </si>
 </sst>
 </file>
@@ -641,7 +641,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2">
         <v>7</v>
@@ -656,7 +656,7 @@
         <v>0.1714285714285714</v>
       </c>
       <c r="G5" s="3">
-        <v>-0.2819594326339022</v>
+        <v>-0.2833666025091003</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
@@ -705,7 +705,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2">
         <v>7</v>
@@ -720,7 +720,7 @@
         <v>0.1714285714285714</v>
       </c>
       <c r="G7" s="3">
-        <v>-0.2833666025091003</v>
+        <v>-0.2819594326339022</v>
       </c>
       <c r="H7" s="2">
         <v>2</v>
@@ -993,7 +993,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C16" s="2">
         <v>5</v>
@@ -1025,7 +1025,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17" s="2">
         <v>5</v>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>23</v>
@@ -1121,7 +1121,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C20" s="2">
         <v>7</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C21" s="2">
         <v>7</v>
